--- a/1. Reporting_Data/IB_Mark-to-Market PnL/AllSymbols/2026/202608/AllSymbols_P&L_20260812.xlsx
+++ b/1. Reporting_Data/IB_Mark-to-Market PnL/AllSymbols/2026/202608/AllSymbols_P&L_20260812.xlsx
@@ -883,20 +883,20 @@
       </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6">
-        <v>11200</v>
+      <c r="A6" t="s">
+        <v>13</v>
       </c>
       <c r="B6">
-        <v>4889</v>
+        <v>545</v>
       </c>
       <c r="C6">
-        <v>21350</v>
+        <v>70900</v>
       </c>
       <c r="D6">
-        <v>-1034.3</v>
+        <v>-38.43</v>
       </c>
       <c r="E6">
-        <v>104380150</v>
+        <v>38640500</v>
       </c>
       <c r="F6" t="s">
         <v>111</v>
@@ -908,24 +908,24 @@
         <v>0.0007</v>
       </c>
       <c r="I6">
-        <v>73066.10000000001</v>
+        <v>27048.35</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7">
-        <v>545</v>
+        <v>243</v>
       </c>
       <c r="C7">
-        <v>70900</v>
+        <v>95800</v>
       </c>
       <c r="D7">
-        <v>-38.43</v>
+        <v>-308.45</v>
       </c>
       <c r="E7">
-        <v>38640500</v>
+        <v>23279400</v>
       </c>
       <c r="F7" t="s">
         <v>111</v>
@@ -937,24 +937,24 @@
         <v>0.0007</v>
       </c>
       <c r="I7">
-        <v>27048.35</v>
+        <v>16295.58</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B8">
-        <v>243</v>
+        <v>1480</v>
       </c>
       <c r="C8">
-        <v>95800</v>
+        <v>97300</v>
       </c>
       <c r="D8">
-        <v>-308.45</v>
+        <v>-1565.52</v>
       </c>
       <c r="E8">
-        <v>23279400</v>
+        <v>144004000</v>
       </c>
       <c r="F8" t="s">
         <v>111</v>
@@ -966,24 +966,24 @@
         <v>0.0007</v>
       </c>
       <c r="I8">
-        <v>16295.58</v>
+        <v>100802.8</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9">
-        <v>1480</v>
+        <v>123</v>
       </c>
       <c r="C9">
-        <v>97300</v>
+        <v>246500</v>
       </c>
       <c r="D9">
-        <v>-1565.52</v>
+        <v>-780.65</v>
       </c>
       <c r="E9">
-        <v>144004000</v>
+        <v>30319500</v>
       </c>
       <c r="F9" t="s">
         <v>111</v>
@@ -995,24 +995,24 @@
         <v>0.0007</v>
       </c>
       <c r="I9">
-        <v>100802.8</v>
+        <v>21223.65</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10">
-        <v>123</v>
+        <v>280</v>
       </c>
       <c r="C10">
-        <v>246500</v>
+        <v>299000</v>
       </c>
       <c r="D10">
-        <v>-780.65</v>
+        <v>-197.45</v>
       </c>
       <c r="E10">
-        <v>30319500</v>
+        <v>83720000</v>
       </c>
       <c r="F10" t="s">
         <v>111</v>
@@ -1024,24 +1024,24 @@
         <v>0.0007</v>
       </c>
       <c r="I10">
-        <v>21223.65</v>
+        <v>58604</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11">
-        <v>280</v>
+        <v>2300</v>
       </c>
       <c r="C11">
-        <v>299000</v>
+        <v>97800</v>
       </c>
       <c r="D11">
-        <v>-197.45</v>
+        <v>-5676.78</v>
       </c>
       <c r="E11">
-        <v>83720000</v>
+        <v>224940000</v>
       </c>
       <c r="F11" t="s">
         <v>111</v>
@@ -1053,65 +1053,65 @@
         <v>0.0007</v>
       </c>
       <c r="I11">
-        <v>58604</v>
+        <v>157458</v>
       </c>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" t="s">
-        <v>18</v>
+      <c r="A12">
+        <v>1109</v>
       </c>
       <c r="B12">
-        <v>2300</v>
+        <v>2000</v>
       </c>
       <c r="C12">
-        <v>97800</v>
+        <v>35</v>
       </c>
       <c r="D12">
-        <v>-5676.78</v>
+        <v>581.08</v>
       </c>
       <c r="E12">
-        <v>224940000</v>
+        <v>70000</v>
       </c>
       <c r="F12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G12" t="s">
         <v>118</v>
       </c>
       <c r="H12">
-        <v>0.0007</v>
+        <v>0.1274</v>
       </c>
       <c r="I12">
-        <v>157458</v>
+        <v>8918</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13">
-        <v>1109</v>
+        <v>11200</v>
       </c>
       <c r="B13">
-        <v>2000</v>
+        <v>4889</v>
       </c>
       <c r="C13">
-        <v>35</v>
+        <v>21350</v>
       </c>
       <c r="D13">
-        <v>581.08</v>
+        <v>-1034.3</v>
       </c>
       <c r="E13">
-        <v>70000</v>
+        <v>104380150</v>
       </c>
       <c r="F13" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G13" t="s">
         <v>118</v>
       </c>
       <c r="H13">
-        <v>0.1274</v>
+        <v>0.0007</v>
       </c>
       <c r="I13">
-        <v>8918</v>
+        <v>73066.10000000001</v>
       </c>
     </row>
     <row r="14" spans="1:9">

--- a/1. Reporting_Data/IB_Mark-to-Market PnL/AllSymbols/2026/202608/AllSymbols_P&L_20260812.xlsx
+++ b/1. Reporting_Data/IB_Mark-to-Market PnL/AllSymbols/2026/202608/AllSymbols_P&L_20260812.xlsx
@@ -883,20 +883,20 @@
       </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" t="s">
-        <v>13</v>
+      <c r="A6">
+        <v>11200</v>
       </c>
       <c r="B6">
-        <v>545</v>
+        <v>4889</v>
       </c>
       <c r="C6">
-        <v>70900</v>
+        <v>21350</v>
       </c>
       <c r="D6">
-        <v>-38.43</v>
+        <v>-1034.3</v>
       </c>
       <c r="E6">
-        <v>38640500</v>
+        <v>104380150</v>
       </c>
       <c r="F6" t="s">
         <v>111</v>
@@ -908,24 +908,24 @@
         <v>0.0007</v>
       </c>
       <c r="I6">
-        <v>27048.35</v>
+        <v>73066.10000000001</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7">
-        <v>243</v>
+        <v>545</v>
       </c>
       <c r="C7">
-        <v>95800</v>
+        <v>70900</v>
       </c>
       <c r="D7">
-        <v>-308.45</v>
+        <v>-38.43</v>
       </c>
       <c r="E7">
-        <v>23279400</v>
+        <v>38640500</v>
       </c>
       <c r="F7" t="s">
         <v>111</v>
@@ -937,24 +937,24 @@
         <v>0.0007</v>
       </c>
       <c r="I7">
-        <v>16295.58</v>
+        <v>27048.35</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B8">
-        <v>1480</v>
+        <v>243</v>
       </c>
       <c r="C8">
-        <v>97300</v>
+        <v>95800</v>
       </c>
       <c r="D8">
-        <v>-1565.52</v>
+        <v>-308.45</v>
       </c>
       <c r="E8">
-        <v>144004000</v>
+        <v>23279400</v>
       </c>
       <c r="F8" t="s">
         <v>111</v>
@@ -966,24 +966,24 @@
         <v>0.0007</v>
       </c>
       <c r="I8">
-        <v>100802.8</v>
+        <v>16295.58</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9">
-        <v>123</v>
+        <v>1480</v>
       </c>
       <c r="C9">
-        <v>246500</v>
+        <v>97300</v>
       </c>
       <c r="D9">
-        <v>-780.65</v>
+        <v>-1565.52</v>
       </c>
       <c r="E9">
-        <v>30319500</v>
+        <v>144004000</v>
       </c>
       <c r="F9" t="s">
         <v>111</v>
@@ -995,24 +995,24 @@
         <v>0.0007</v>
       </c>
       <c r="I9">
-        <v>21223.65</v>
+        <v>100802.8</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10">
-        <v>280</v>
+        <v>123</v>
       </c>
       <c r="C10">
-        <v>299000</v>
+        <v>246500</v>
       </c>
       <c r="D10">
-        <v>-197.45</v>
+        <v>-780.65</v>
       </c>
       <c r="E10">
-        <v>83720000</v>
+        <v>30319500</v>
       </c>
       <c r="F10" t="s">
         <v>111</v>
@@ -1024,24 +1024,24 @@
         <v>0.0007</v>
       </c>
       <c r="I10">
-        <v>58604</v>
+        <v>21223.65</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11">
-        <v>2300</v>
+        <v>280</v>
       </c>
       <c r="C11">
-        <v>97800</v>
+        <v>299000</v>
       </c>
       <c r="D11">
-        <v>-5676.78</v>
+        <v>-197.45</v>
       </c>
       <c r="E11">
-        <v>224940000</v>
+        <v>83720000</v>
       </c>
       <c r="F11" t="s">
         <v>111</v>
@@ -1053,65 +1053,65 @@
         <v>0.0007</v>
       </c>
       <c r="I11">
+        <v>58604</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12">
+        <v>2300</v>
+      </c>
+      <c r="C12">
+        <v>97800</v>
+      </c>
+      <c r="D12">
+        <v>-5676.78</v>
+      </c>
+      <c r="E12">
+        <v>224940000</v>
+      </c>
+      <c r="F12" t="s">
+        <v>111</v>
+      </c>
+      <c r="G12" t="s">
+        <v>118</v>
+      </c>
+      <c r="H12">
+        <v>0.0007</v>
+      </c>
+      <c r="I12">
         <v>157458</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="A12">
-        <v>1109</v>
-      </c>
-      <c r="B12">
-        <v>2000</v>
-      </c>
-      <c r="C12">
-        <v>35</v>
-      </c>
-      <c r="D12">
-        <v>581.08</v>
-      </c>
-      <c r="E12">
-        <v>70000</v>
-      </c>
-      <c r="F12" t="s">
-        <v>112</v>
-      </c>
-      <c r="G12" t="s">
-        <v>118</v>
-      </c>
-      <c r="H12">
-        <v>0.1274</v>
-      </c>
-      <c r="I12">
-        <v>8918</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13">
-        <v>11200</v>
+        <v>1109</v>
       </c>
       <c r="B13">
-        <v>4889</v>
+        <v>2000</v>
       </c>
       <c r="C13">
-        <v>21350</v>
+        <v>35</v>
       </c>
       <c r="D13">
-        <v>-1034.3</v>
+        <v>581.08</v>
       </c>
       <c r="E13">
-        <v>104380150</v>
+        <v>70000</v>
       </c>
       <c r="F13" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G13" t="s">
         <v>118</v>
       </c>
       <c r="H13">
-        <v>0.0007</v>
+        <v>0.1274</v>
       </c>
       <c r="I13">
-        <v>73066.10000000001</v>
+        <v>8918</v>
       </c>
     </row>
     <row r="14" spans="1:9">
